--- a/data/trans_orig/IP07A04-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A04-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7473</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17815</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24666</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>21883</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13775</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27318</t>
+          <t>26925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28150</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44215</t>
+          <t>44767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>15003</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17623</t>
+          <t>17479</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31104</t>
+          <t>30383</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35822</t>
+          <t>35885</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54605</t>
+          <t>54348</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22599</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32383</t>
+          <t>33169</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,9%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22785</t>
+          <t>22352</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>17477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31852</t>
+          <t>31784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12459</t>
+          <t>11758</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24041</t>
+          <t>23577</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>14741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19535</t>
+          <t>19131</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35160</t>
+          <t>34688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23097</t>
+          <t>22090</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37728</t>
+          <t>36824</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38212</t>
+          <t>37455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56650</t>
+          <t>56469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24465</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39390</t>
+          <t>39431</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>20818</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>34142</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48651</t>
+          <t>48658</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>68129</t>
+          <t>69534</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>34,22%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6512</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16731</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11288</t>
+          <t>11670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22872</t>
+          <t>23730</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20382</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36261</t>
+          <t>35849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21811</t>
+          <t>22331</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20971</t>
+          <t>21656</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35740</t>
+          <t>35695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>54441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21727</t>
+          <t>20712</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15587</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19131</t>
+          <t>19349</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33680</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8754</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18166</t>
+          <t>18757</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14153</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15652</t>
+          <t>16006</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29534</t>
+          <t>29159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9964</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20796</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>11794</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23096</t>
+          <t>23108</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>24829</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>40226</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>8293</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18346</t>
+          <t>18768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26606</t>
+          <t>26868</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15750</t>
+          <t>15934</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>21979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20334</t>
+          <t>20030</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34922</t>
+          <t>33880</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25186</t>
+          <t>25327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20158</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23731</t>
+          <t>24739</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41510</t>
+          <t>41880</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29149</t>
+          <t>28939</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9751</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22084</t>
+          <t>21159</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>28284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45943</t>
+          <t>47384</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35821</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20436</t>
+          <t>20501</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35049</t>
+          <t>35620</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>45658</t>
+          <t>45724</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>67151</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>14632</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14047</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>27842</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21586</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>38082</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21494</t>
+          <t>22048</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>28943</t>
+          <t>28959</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28121</t>
+          <t>28597</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45971</t>
+          <t>47056</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50572</t>
+          <t>51842</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>74204</t>
+          <t>74318</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>30021</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48628</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>86384</t>
+          <t>86815</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>116815</t>
+          <t>116827</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>66468</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93486</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>50730</t>
+          <t>50747</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>72556</t>
+          <t>74141</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>123997</t>
+          <t>126304</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>158374</t>
+          <t>159235</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>82020</t>
+          <t>81727</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107992</t>
+          <t>107388</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>81438</t>
+          <t>81067</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>107225</t>
+          <t>107778</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>172884</t>
+          <t>170972</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>210288</t>
+          <t>208064</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,32%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26799</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45152</t>
+          <t>44060</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>78504</t>
+          <t>77970</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>86481</t>
+          <t>86857</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>115890</t>
+          <t>116769</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>39119</t>
+          <t>39419</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>59507</t>
+          <t>61079</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>70983</t>
+          <t>70448</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>96422</t>
+          <t>95761</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>116142</t>
+          <t>116446</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>148654</t>
+          <t>148827</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10160</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>14817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18144</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34118</t>
+          <t>34153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>17737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>10435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21416</t>
+          <t>21884</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19694</t>
+          <t>20292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34400</t>
+          <t>35162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>20786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>24058</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23937</t>
+          <t>23960</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>40759</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7046</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17177</t>
+          <t>17613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16094</t>
+          <t>15697</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31261</t>
+          <t>30290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14656</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27093</t>
+          <t>26820</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24201</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41128</t>
+          <t>41334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25107</t>
+          <t>25148</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23711</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>22488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19972</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>22214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38303</t>
+          <t>38726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21428</t>
+          <t>21958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36082</t>
+          <t>35929</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>15637</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28304</t>
+          <t>28501</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40256</t>
+          <t>41358</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60979</t>
+          <t>60359</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21006</t>
+          <t>20016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19888</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20418</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36531</t>
+          <t>36332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>15188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23670</t>
+          <t>24155</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>38706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43565</t>
+          <t>42633</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63292</t>
+          <t>63226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>12031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19411</t>
+          <t>18766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23130</t>
+          <t>23564</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>39165</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19541</t>
+          <t>19972</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>21437</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>21628</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37768</t>
+          <t>37209</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20953</t>
+          <t>20821</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11264</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22009</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22734</t>
+          <t>23905</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38834</t>
+          <t>39589</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4466</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>21164</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>9349</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11712</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22423</t>
+          <t>23613</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23275</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38783</t>
+          <t>38603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20625</t>
+          <t>20472</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35961</t>
+          <t>35399</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11879</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>24749</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36025</t>
+          <t>35586</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56682</t>
+          <t>54857</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>29,74%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>16861</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32129</t>
+          <t>31851</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21147</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>29043</t>
+          <t>30565</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48844</t>
+          <t>49821</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18906</t>
+          <t>19613</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34344</t>
+          <t>34895</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18968</t>
+          <t>17490</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32820</t>
+          <t>32144</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>41815</t>
+          <t>41767</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>62376</t>
+          <t>63745</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2185</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22048</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13085</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27954</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>14459</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27280</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21644</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38994</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>66826</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>92452</t>
+          <t>91765</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>46533</t>
+          <t>45506</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>68682</t>
+          <t>68107</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>120395</t>
+          <t>119886</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>155142</t>
+          <t>152392</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,33%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54437</t>
+          <t>54333</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77657</t>
+          <t>79489</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>47777</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>69842</t>
+          <t>70884</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>105746</t>
+          <t>106867</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>139984</t>
+          <t>139708</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>71869</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>97839</t>
+          <t>97399</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>67149</t>
+          <t>68539</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94246</t>
+          <t>94108</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>146845</t>
+          <t>147013</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>183305</t>
+          <t>182933</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>28432</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48846</t>
+          <t>47411</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>38943</t>
+          <t>38706</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59894</t>
+          <t>59590</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>70402</t>
+          <t>72512</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>99130</t>
+          <t>99753</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>45299</t>
+          <t>45333</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>67988</t>
+          <t>67829</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>75103</t>
+          <t>74891</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>101677</t>
+          <t>102079</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>127323</t>
+          <t>124729</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>161553</t>
+          <t>160392</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de preocuparse por su aspecto en 2016 (tasa de respuesta: 98,82%)</t>
+          <t>Menores según la frecuencia de preocuparse por su aspecto, percibida por el adulto en 2016 (tasa de respuesta: 98,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12624</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25154</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17886</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22717</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39298</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7292</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>18320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>9541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>21478</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>19753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36583</t>
+          <t>36488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10960</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24424</t>
+          <t>22689</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>13256</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32819</t>
+          <t>33088</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25013</t>
+          <t>26026</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18292</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34123</t>
+          <t>34199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,79%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28497</t>
+          <t>28056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27997</t>
+          <t>28658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46237</t>
+          <t>45927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>31409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15536</t>
+          <t>15810</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29371</t>
+          <t>29965</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35832</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55797</t>
+          <t>55787</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32254</t>
+          <t>32054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>12322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25752</t>
+          <t>24624</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>34098</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52680</t>
+          <t>53033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,81%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30275</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22681</t>
+          <t>22953</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30271</t>
+          <t>30559</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>48080</t>
+          <t>47945</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,43%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21814</t>
+          <t>22485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>17172</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32274</t>
+          <t>30597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31009</t>
+          <t>31020</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49216</t>
+          <t>49248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13217</t>
+          <t>12882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>25773</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>21362</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>36342</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58510</t>
+          <t>57945</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23441</t>
+          <t>22990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38767</t>
+          <t>39968</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>10926</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22044</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7539</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21487</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37385</t>
+          <t>38533</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9109</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>20769</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14639</t>
+          <t>14561</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26936</t>
+          <t>26849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26865</t>
+          <t>26315</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44779</t>
+          <t>43673</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14112</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25479</t>
+          <t>24675</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10691</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>15687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29027</t>
+          <t>28372</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28328</t>
+          <t>28912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46517</t>
+          <t>46324</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18440</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34010</t>
+          <t>33949</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25906</t>
+          <t>25726</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34258</t>
+          <t>34322</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55049</t>
+          <t>54492</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>29260</t>
+          <t>29309</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24097</t>
+          <t>24925</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30419</t>
+          <t>29525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>49623</t>
+          <t>49956</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28920</t>
+          <t>28702</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28845</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>33239</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>53114</t>
+          <t>52352</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23364</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14324</t>
+          <t>14822</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>28010</t>
+          <t>28702</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27885</t>
+          <t>28169</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47242</t>
+          <t>47641</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31857</t>
+          <t>32051</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32590</t>
+          <t>32206</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>37486</t>
+          <t>37567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58470</t>
+          <t>57831</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>71226</t>
+          <t>70523</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>98116</t>
+          <t>97732</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>54322</t>
+          <t>53435</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>79978</t>
+          <t>79024</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>134098</t>
+          <t>133352</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>170419</t>
+          <t>168585</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>61167</t>
+          <t>61310</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>86473</t>
+          <t>86487</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>52083</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>76713</t>
+          <t>75911</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>119994</t>
+          <t>120892</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>155770</t>
+          <t>155668</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>63180</t>
+          <t>63387</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>87819</t>
+          <t>88962</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>52978</t>
+          <t>51784</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>76352</t>
+          <t>77913</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>120948</t>
+          <t>122928</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>157065</t>
+          <t>157261</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>58947</t>
+          <t>61045</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>60032</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>85935</t>
+          <t>85814</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>105440</t>
+          <t>104300</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>138798</t>
+          <t>139384</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>62067</t>
+          <t>60844</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>86540</t>
+          <t>85661</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>81576</t>
+          <t>82233</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>109938</t>
+          <t>109746</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>150267</t>
+          <t>150346</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>188656</t>
+          <t>189458</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
